--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2169811320754717</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="B2">
-        <v>0.04166666666666666</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2482269503546099</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="D2">
-        <v>0.8153846153846154</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="E2">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F2">
+        <v>21</v>
+      </c>
+      <c r="G2">
         <v>24</v>
-      </c>
-      <c r="G2">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2105263157894737</v>
+        <v>0.21875</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3142857142857143</v>
+        <v>0.3098591549295774</v>
       </c>
       <c r="D2">
-        <v>0.8275862068965517</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="E2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
